--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-dicom-study-metadata.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-dicom-study-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T12:47:35+00:00</t>
+    <t>2026-05-07T13:30:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-dicom-study-metadata.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-dicom-study-metadata.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Modèle logique métier - FR LM DICOM Study Metadata</t>
+    <t>Logical model - FR LM DICOM Study Metadata</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T13:30:39+00:00</t>
+    <t>2026-05-12T13:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -375,7 +375,7 @@
     <t>fr-lm-section.entry</t>
   </si>
   <si>
-    <t>fr-lm-dicom-study-metadata.entry.examenImagerie</t>
+    <t>fr-lm-dicom-study-metadata.entry.imagingStudy</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-imaging-study
@@ -718,7 +718,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.58203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.15234375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
